--- a/Översikt OLOFSTRÖM.xlsx
+++ b/Översikt OLOFSTRÖM.xlsx
@@ -601,7 +601,7 @@
         <v>45212</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44809</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>45629</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45268</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>46029</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>44559</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45581</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45107</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45583</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>45641</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>44880</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>44568</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>45141</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45203</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45583</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45548</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>45548</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45098</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45117</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>44858</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>45733</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>46050</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>46070</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45625</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45681</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>46073</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>46087</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>44726</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>44610</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>44726</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44503</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44610</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44610</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44755</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44587</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44558</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44572</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>44853</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>44613</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>44567</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>44551</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>44649</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44649</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44516</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>44613</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>44613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>44613</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>44699</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>44469</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>44551</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44551</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44866</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44551</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44551</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44551</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44747</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44496</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44610</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44686</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44592</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44634</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45166</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>45597</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>45162</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>45169</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44582</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>45271</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>45516</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45548</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>45700</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>45002</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44581</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45180</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45246</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>45560</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44473</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>44531</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         <v>45552</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>45693</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         <v>45747</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>45747</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7869,7 +7869,7 @@
         <v>45645</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44858</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45608</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>45183</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8161,7 +8161,7 @@
         <v>45168</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>45071</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>45177</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>45548</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44971</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>45582</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>45274</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45544</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         <v>44809</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>45575</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>44873</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44970</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>44858</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>44858</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>44470</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>45623</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>45180</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>45623</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>45268</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45197</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>45221</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>45203</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>45282</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>45548</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9918,7 +9918,7 @@
         <v>45614</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>45233</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>44832</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>45775</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>44942</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10288,7 +10288,7 @@
         <v>44951</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>45707</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>44889</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>45709</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>45114</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>45818</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>44935</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>45111</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>45198</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45887</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>45891</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>45629</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>45896</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>45896</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>45896</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>45898</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>45898</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>45755</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>45902</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45902</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>45775</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45707</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>45707</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>45903</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>45936</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>45265</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>45910</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>45497</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12332,7 +12332,7 @@
         <v>45793</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>45818</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>44626</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>45274</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>45166</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>44866</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>45012</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>44704</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>45925</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>45925</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>45699</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>46003</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13213,7 +13213,7 @@
         <v>45975</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>46143</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>45930</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>45723</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45551</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>44935</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>45371</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>45706</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45938</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>45520</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>45520</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
         <v>45940</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45594</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>45719</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45195</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>45594</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>44791</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45407</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45602</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>44811</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>45956</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>45006</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>45112</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45268</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>44929</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>45341</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45965</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45963</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45548</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45548</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>45967</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>45011</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>45565</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>45975</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>45238</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>44879</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>45245</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45720</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45849</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45271</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45271</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>45268</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>45268</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>45700</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>45988</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>45852</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>44531</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16684,7 +16684,7 @@
         <v>44704</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16757,7 +16757,7 @@
         <v>45274</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>44552</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>45698</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>45166</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
         <v>46013</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>44876</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>45036</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>46169</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>45742</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>45583</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>45268</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>46027</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>46027</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>46027</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>44992</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>45401</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44873</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18003,7 +18003,7 @@
         <v>45595</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45247</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>45247</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18222,7 +18222,7 @@
         <v>46042</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>44949</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18368,7 +18368,7 @@
         <v>46045</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>45225</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18519,7 +18519,7 @@
         <v>45274</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>45274</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45197</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>44468</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18811,7 +18811,7 @@
         <v>44858</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>46050</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18957,7 +18957,7 @@
         <v>46056</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
         <v>45282</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19103,7 +19103,7 @@
         <v>44965</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         <v>44965</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         <v>45090</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>46065</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19395,7 +19395,7 @@
         <v>46059</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>46059</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45005</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>46070</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>46070</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>46070</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45338</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>45338</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45338</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>46078</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>44748</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45197</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>44971</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20344,7 +20344,7 @@
         <v>45701</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20417,7 +20417,7 @@
         <v>44805</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20490,7 +20490,7 @@
         <v>44536</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>46097</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>45233</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>45588</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>46104</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
         <v>45699</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>46106</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>46070</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>44590</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45120</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>46202</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>45195</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>46119</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>46120</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>45194</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45274</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45274</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>46125</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>44743</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>46202</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>46127</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>45385</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>45527</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>45575</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>45141</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22325,7 +22325,7 @@
         <v>44862</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>45849</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22471,7 +22471,7 @@
         <v>44970</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>45320</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>45271</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>45883</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>45133</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         <v>45603</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>45707</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -22982,7 +22982,7 @@
         <v>45008</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>45104</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44816</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>44622</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>45233</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23347,7 +23347,7 @@
         <v>44550</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45163</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>44789</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>45593</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>45282</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45078</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23785,7 +23785,7 @@
         <v>45019</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>45204</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45204</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>46255</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45639</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>45141</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>46258</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>46097</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24374,7 +24374,7 @@
         <v>44616</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24447,7 +24447,7 @@
         <v>45700</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>45180</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>44851</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>46261</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>45243</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>44922</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>44974</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -24958,7 +24958,7 @@
         <v>44974</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>45723</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25104,7 +25104,7 @@
         <v>45571</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>45032</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>45320</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>45594</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>45602</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45693</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45112</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>44984</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>45282</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45107</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25839,7 +25839,7 @@
         <v>45338</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>46269</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>45694</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26058,7 +26058,7 @@
         <v>46276</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>45726</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>45583</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>45338</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>45698</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>46280</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45733</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>46280</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>46280</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45796</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>46283</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>46282</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45733</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>46282</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45698</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45803</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>45803</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>45432</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45827</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>45742</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45827</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45827</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27714,7 +27714,7 @@
         <v>45868</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>44469</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>45261</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>44966</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45016</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>45827</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>45827</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45956</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>45956</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>44543</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>

--- a/Översikt OLOFSTRÖM.xlsx
+++ b/Översikt OLOFSTRÖM.xlsx
@@ -601,7 +601,7 @@
         <v>45212</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44809</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>45629</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45268</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45133</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>44559</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45581</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45641</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45583</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>45107</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45117</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>46050</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45681</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>46070</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45583</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>45098</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>44568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>45733</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45141</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45548</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45548</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>45203</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45195</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44858</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44880</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>45625</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>46073</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>46087</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44610</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>44726</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44503</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>44610</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44610</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44755</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>44587</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>44572</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44558</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44853</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44613</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>44567</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44551</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44866</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44649</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>44649</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>44516</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>44613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>44613</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>44699</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>44469</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>44551</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>44551</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44866</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44551</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44551</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>44551</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44496</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>44610</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44686</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>44592</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>44634</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>45194</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>45032</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>44992</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>45701</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>44970</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45320</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>45243</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>45271</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45268</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>46027</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>46027</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>46027</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44942</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>45796</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44531</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>45887</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44873</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45548</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>45891</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45195</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44984</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>46042</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>45896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>45371</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45896</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>45896</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45898</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>45898</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>45775</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>45902</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45902</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>45548</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45698</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45733</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>45903</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>46050</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45560</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45910</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>46056</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45803</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>46065</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>45432</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>46059</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44971</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>46059</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>45803</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>46070</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>44616</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>45925</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>45925</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>45112</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>45699</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>46078</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45930</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44971</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>44951</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>45247</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>44876</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44970</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>44974</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>44974</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>45588</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>45548</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>45938</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>45940</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>46097</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>45719</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>45225</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>44622</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>46104</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>46106</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>46070</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>45268</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>45956</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>45623</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>46119</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>45963</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>46120</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>44935</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>46125</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>45629</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>45965</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>45594</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>45593</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>44743</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>45967</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>46127</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>45602</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>45639</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>45975</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>45238</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>44862</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>44704</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>45133</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>45645</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44791</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>45818</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45849</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45775</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>45988</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>45709</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>45693</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>45883</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45707</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>45936</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>45168</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>45169</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>45793</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45747</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>45747</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>45707</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45197</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45742</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>46013</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>45497</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>44879</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45071</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>45246</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>45565</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45827</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>45827</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45723</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>45827</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>45818</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>45742</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>45338</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>44473</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>46003</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>46143</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>45975</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>45090</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>45594</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>44468</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>45700</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45265</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>45112</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>45107</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>45849</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>44889</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45011</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45852</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>45385</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45233</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45282</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>45197</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>46169</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>45582</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>45868</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>44858</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45575</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45338</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>45338</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45338</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>45720</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>45268</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>45548</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45401</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>45166</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45595</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>45180</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45274</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>45180</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44581</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>45120</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>45527</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45602</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45698</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45203</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>45008</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>44582</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>44832</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45551</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>45594</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>45166</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45552</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>45177</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>46202</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>44748</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>46202</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         <v>44805</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45583</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45623</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45141</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44858</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>46255</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>46258</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>45693</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>45700</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45700</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>46097</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45166</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>44704</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>46261</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45282</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45707</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45707</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45198</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>44858</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>45247</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>44816</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45520</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45520</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45282</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>45320</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45271</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>45282</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>46269</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>45274</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45274</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>44873</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>46276</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45341</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>46280</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>46280</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>46280</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>46283</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>46286</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>45597</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>46282</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>46284</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44552</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>46282</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45548</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>46286</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>44851</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>44626</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45268</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44935</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>45245</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>44811</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>45002</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>45180</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>45197</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>45111</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>44858</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44590</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>45006</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>44550</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>45005</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45274</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>45614</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>45274</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>45114</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>45104</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>44470</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>44929</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45755</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45575</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>44949</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>45407</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45012</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45078</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45516</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45544</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>45019</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>44809</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>45162</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>45723</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45233</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45141</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>45608</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>44531</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45233</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>45699</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44922</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45221</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>44866</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>44965</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>44965</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>45271</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45183</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45271</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45268</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>44789</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45274</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>45571</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45163</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45204</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>45204</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>45195</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>45603</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45036</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45706</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44536</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45274</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45694</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>45583</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45698</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45733</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45726</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45338</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>44469</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>45261</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44966</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45016</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45827</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28262,7 +28262,7 @@
         <v>45827</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45956</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45956</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44543</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>

--- a/Översikt OLOFSTRÖM.xlsx
+++ b/Översikt OLOFSTRÖM.xlsx
@@ -601,7 +601,7 @@
         <v>45212</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44809</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>46029</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>45629</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45268</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>45133</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>44559</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45581</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>45641</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>45583</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>45107</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>45117</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>46050</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>45681</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>46070</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>45583</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>45098</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>44568</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>45733</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>45141</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45548</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>45548</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>46286</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         <v>45203</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45195</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44858</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>44880</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>45625</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>46073</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>46087</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>44610</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>44726</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44503</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         <v>44610</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4314,7 +4314,7 @@
         <v>44610</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>44755</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>44587</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         <v>44572</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44558</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44853</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44613</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>44567</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44551</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44866</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44649</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>44649</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         <v>44516</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>44613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>44613</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>44699</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>44469</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>44551</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>44551</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44866</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44551</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44551</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>44551</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44496</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>44610</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>44686</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>44592</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>44634</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6514,7 +6514,7 @@
         <v>45194</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>45032</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         <v>44992</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
         <v>45701</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>44970</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>45320</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>45243</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>45271</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45268</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>46027</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>46027</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>46027</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44942</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>45796</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44531</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>45887</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44873</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45548</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>45891</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45195</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44984</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>46042</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>45896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>45371</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45896</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>45896</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45898</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>45898</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>45775</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>45902</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45902</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>45548</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45698</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45733</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>45903</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>46050</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9152,7 +9152,7 @@
         <v>45560</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>45910</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>46056</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         <v>45803</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>46065</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>45432</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>46059</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44971</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>46059</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>45803</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>46070</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>44616</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>45925</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>45925</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>45112</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>45699</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>46078</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45930</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44971</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>44951</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>45247</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>44876</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44970</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>44974</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>44974</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>45588</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>45548</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>45938</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>45940</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>46097</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>45719</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>45225</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>44622</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>46104</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>46106</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>46070</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>45268</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>45956</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>45623</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>46119</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>45963</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>46120</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>44935</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>46125</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>45629</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>45965</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>45594</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>45593</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>44743</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>45967</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>46127</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>45602</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>45639</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>45975</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>45238</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>44862</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>44704</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>45133</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>45645</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44791</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>45818</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45849</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45775</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>45988</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>45709</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>45693</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>45883</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45707</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>45936</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>45168</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>45169</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>45793</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45747</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>45747</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>45707</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45197</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45742</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>46013</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>45497</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>44879</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45071</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>45246</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>45565</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45827</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>45827</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45723</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>45827</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>45818</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>45742</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>45338</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>44473</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>46003</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>46143</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>45975</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>45090</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>45594</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>44468</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>45700</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45265</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>45112</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>45107</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>45849</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>44889</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45011</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45852</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>45385</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45233</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45282</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>45197</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>46169</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>45582</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>45868</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>44858</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         <v>45575</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45338</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17592,7 +17592,7 @@
         <v>45338</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17665,7 +17665,7 @@
         <v>45338</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>45720</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
         <v>45268</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>45548</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45401</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>45166</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45595</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>45180</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45274</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>45180</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>44581</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>45120</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>45527</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>45602</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45698</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45203</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>45008</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>44582</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>44832</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19057,7 +19057,7 @@
         <v>45551</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>45594</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>45166</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45552</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>45177</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>46202</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>44748</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>46202</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         <v>44805</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45583</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45623</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45141</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44858</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20006,7 +20006,7 @@
         <v>46255</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>46258</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>45693</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>45700</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20303,7 +20303,7 @@
         <v>45700</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>46097</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45166</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>44704</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>46261</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45282</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45707</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45707</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45198</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>44858</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>45247</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>44816</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45520</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45520</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45282</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>45320</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45271</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>45282</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>46269</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>45274</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45274</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>44873</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>46276</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45341</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>46280</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>46280</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>46280</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>46283</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>46286</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>45597</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>46282</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>46284</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44552</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>46282</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45548</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>46286</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>44851</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>44626</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45268</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>44935</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>45245</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>44811</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>45002</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>45180</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>45197</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>45111</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>44858</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>44590</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>45006</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>44550</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>45005</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         <v>45274</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24149,7 +24149,7 @@
         <v>45614</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>45274</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>45114</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>45104</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>44470</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>44929</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45755</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45575</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24733,7 +24733,7 @@
         <v>44949</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24806,7 +24806,7 @@
         <v>45407</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45012</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24952,7 +24952,7 @@
         <v>45078</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25025,7 +25025,7 @@
         <v>45516</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45544</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25171,7 +25171,7 @@
         <v>45019</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>44809</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>45162</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>45723</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45233</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45141</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>45608</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25682,7 +25682,7 @@
         <v>44531</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45233</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>45699</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44922</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>45221</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>44866</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>44965</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>44965</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>45271</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45183</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45271</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45268</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>44789</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45274</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>45571</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45163</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45204</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>45204</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>45195</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>45603</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>45036</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45706</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44536</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45274</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>45694</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>45583</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45698</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45733</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45726</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45338</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>44469</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>45261</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>44966</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28111,7 +28111,7 @@
         <v>45016</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45827</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28262,7 +28262,7 @@
         <v>45827</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45956</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45956</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>44543</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>

--- a/Översikt OLOFSTRÖM.xlsx
+++ b/Översikt OLOFSTRÖM.xlsx
@@ -601,7 +601,7 @@
         <v>45212</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44809</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>45629</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45268</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44559</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45583</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>45641</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45581</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45107</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45625</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44568</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>45141</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>45681</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>46050</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>46070</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>45548</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45548</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45098</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45117</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45583</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44858</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45733</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>46286</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>46073</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>46087</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>44726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>44726</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44503</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>44610</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44610</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>44755</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>44587</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>44558</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>44853</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>44613</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44567</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>44551</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>44866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>44649</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>44649</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>44516</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>44613</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>44613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>44613</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>44699</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>44551</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>44551</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>44866</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>44551</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>44551</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>44551</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>44747</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44496</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44610</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44686</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44634</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>45166</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>45597</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>45560</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45162</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>45169</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44582</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>45271</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>45700</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>45548</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>45002</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>45180</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>45516</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>45726</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>45583</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>45338</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>45698</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>45733</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>44581</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>45246</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44473</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44531</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>45552</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>45645</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>45747</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>45747</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>45693</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>46013</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44858</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>46027</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>45608</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>46027</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45891</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>45896</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>45183</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>45896</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45896</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45898</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45898</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>45071</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45902</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45902</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45168</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45775</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45910</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>46042</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45796</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45733</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>45803</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>45803</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>45432</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>46050</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>45925</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>45925</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>45699</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>44971</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>46056</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>45548</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45177</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45930</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>46065</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>46059</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>46059</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>46070</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>45938</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>45582</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         <v>45274</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>45940</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>45544</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>45575</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>45719</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>46078</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>44809</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>44873</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>44970</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>44858</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>44858</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>45623</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>45956</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>45965</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>45963</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45623</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>45268</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>46097</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>45967</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>45180</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>45221</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>45197</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>45203</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12851,7 +12851,7 @@
         <v>45282</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>45233</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>45975</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>46104</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>45548</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>46106</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>46070</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45614</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44832</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>46119</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>46120</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44942</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44951</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45707</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45827</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>46125</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44743</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>44889</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>46127</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>45742</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>45827</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45827</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45114</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>44862</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>44935</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>45111</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45198</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45849</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45629</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>45883</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>45133</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>45755</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>45775</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45707</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>45707</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45709</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45265</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45818</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>44626</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45274</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45166</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>44866</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45012</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>44704</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>45723</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>45551</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>44935</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45936</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45371</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>45706</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45497</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>45793</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45818</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45520</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45520</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45868</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45594</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45195</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>46003</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45975</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45594</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>46143</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44791</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45407</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>45602</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>44811</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45006</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>45112</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45268</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>44929</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45341</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45849</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>45548</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45548</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>45011</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45565</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45852</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45238</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>44879</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45245</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>45720</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>46169</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>45271</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>45271</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>45268</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>45268</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>45700</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>44531</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45887</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>44704</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45274</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44552</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45698</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>45166</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>44876</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45036</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45742</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45583</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>46202</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45268</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>46202</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>44992</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45401</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44873</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45595</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45247</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45247</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44949</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>46258</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45225</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>46097</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45274</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45274</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45197</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>44858</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>46261</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45282</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44965</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>44965</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45090</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45005</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>46269</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>45338</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45338</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45338</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>44748</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45197</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>46276</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>46280</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>46280</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>46280</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44971</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45701</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>44805</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>44536</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>46283</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>46282</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>46282</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45233</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45588</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45699</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44590</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>45120</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46286</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>46286</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>46284</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45195</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>45194</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>45274</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>45274</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>45385</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>45527</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45575</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>45141</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>46293</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44970</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45320</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45271</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>46293</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>45903</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>45603</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45707</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>46297</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>45008</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45104</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44816</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>46255</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>44622</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45233</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>44550</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>45163</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>44789</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45593</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45282</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45078</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>45019</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45204</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45204</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45639</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45141</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44616</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45700</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45180</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>44851</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>45243</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>44922</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>44974</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>44974</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>45723</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>45571</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>45032</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>45320</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45594</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45602</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>45693</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>45112</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>44984</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45282</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45107</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>45338</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         <v>45694</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>45261</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>44966</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>45016</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45827</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45827</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>45956</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>45956</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44543</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>

--- a/Översikt OLOFSTRÖM.xlsx
+++ b/Översikt OLOFSTRÖM.xlsx
@@ -601,7 +601,7 @@
         <v>45212</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44809</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>45629</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45268</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44559</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45583</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>45641</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45581</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45107</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45625</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44568</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>45141</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>45681</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>46050</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>46070</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>45548</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45548</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45098</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45117</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45583</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>44858</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45733</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>46286</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>46073</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>46087</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>44610</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>44726</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>44726</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44503</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>44610</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44610</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>44755</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>44587</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>44572</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>44558</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>44853</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>44613</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>44567</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>44551</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>44866</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>44649</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>44649</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>44516</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>44613</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>44613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>44613</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>44699</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>44551</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
         <v>44551</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>44866</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>44551</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>44551</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>44551</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>44747</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44496</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44610</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44686</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44634</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>45166</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>45597</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>45560</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>45162</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>45169</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         <v>44582</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>45271</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>45700</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>45548</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>45002</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>45180</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>45516</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>45726</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>45583</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>45338</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>45698</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>45733</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>44581</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>45246</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44473</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44531</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         <v>45552</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>45645</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>45747</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         <v>45747</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         <v>45693</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>46013</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44858</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>46027</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8451,7 +8451,7 @@
         <v>45608</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>46027</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>45891</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>45896</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>45183</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>45896</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45896</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45898</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45898</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9108,7 +9108,7 @@
         <v>45071</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>45902</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>45902</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45168</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45775</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45910</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>46042</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9619,7 +9619,7 @@
         <v>45796</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45733</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>45803</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>45803</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>45432</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>46050</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>45925</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>45925</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>45699</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>44971</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>46056</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>45548</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45177</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45930</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>46065</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>46059</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>46059</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>46070</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>45938</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>45582</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         <v>45274</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>45940</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>45544</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>45575</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         <v>45719</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>46078</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>44809</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
         <v>44873</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>44970</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         <v>44858</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         <v>44858</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>45623</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>45956</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         <v>45965</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>45963</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45623</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>45268</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>46097</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>45967</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>45180</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>45221</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>45197</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>45203</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12851,7 +12851,7 @@
         <v>45282</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>45233</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>45975</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>46104</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>45548</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>46106</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>46070</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45614</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>44832</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>46119</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>46120</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44942</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44951</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45707</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45827</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>46125</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44743</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>44889</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>46127</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>45742</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>45827</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>45827</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45114</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>44862</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>44935</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>45111</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45198</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45849</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45629</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>45883</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>45133</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>45755</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>45775</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45707</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>45707</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45709</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45265</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45818</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>44626</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45274</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45166</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>44866</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>45012</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>44704</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>45723</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>45551</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>44935</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45936</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45371</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>45706</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>45497</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>45793</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>45818</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45520</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45520</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45868</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45594</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45195</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>46003</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45975</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45594</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>46143</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>44791</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>45407</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>45602</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>44811</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45006</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>45112</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>45268</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>44929</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45341</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45849</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>45548</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>45548</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
         <v>45011</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18361,7 +18361,7 @@
         <v>45565</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18434,7 +18434,7 @@
         <v>45852</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>45238</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18580,7 +18580,7 @@
         <v>44879</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>45245</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>45720</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>46169</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>45271</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>45271</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>45268</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>45268</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>45700</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>44531</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45887</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>44704</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45274</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>44552</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45698</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>45166</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>44876</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45036</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45742</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45583</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>46202</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45268</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>46202</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>44992</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>45401</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44873</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45595</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45247</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45247</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44949</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>46258</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45225</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>46097</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45274</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>45274</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>45197</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>44858</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>46261</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>45282</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44965</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>44965</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>45090</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45005</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>46269</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>45338</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45338</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45338</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>44748</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>45197</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>46276</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>46280</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>46280</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>46280</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>44971</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>45701</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>44805</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>44536</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>46283</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>46282</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>46282</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45233</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45588</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>45699</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44590</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>45120</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>46286</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>46286</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>46284</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45195</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>45194</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>45274</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>45274</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>45385</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>45527</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45575</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>45141</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>46293</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>44970</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>45320</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45271</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24495,7 +24495,7 @@
         <v>46293</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>45903</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24646,7 +24646,7 @@
         <v>45603</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24719,7 +24719,7 @@
         <v>45707</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>46297</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>45008</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45104</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44816</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25089,7 +25089,7 @@
         <v>46255</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>44622</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>45233</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>44550</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>45163</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>44789</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45593</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45282</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45078</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>45019</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45204</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45204</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45639</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45141</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44616</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45700</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45180</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>44851</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>45243</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>44922</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>44974</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>44974</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>45723</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>45571</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>45032</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>45320</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45594</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45602</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>45693</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>45112</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>44984</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45282</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45107</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27503,7 +27503,7 @@
         <v>45338</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         <v>45694</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>45261</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27722,7 +27722,7 @@
         <v>44966</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27795,7 +27795,7 @@
         <v>45016</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45827</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45827</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>45956</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>45956</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>44543</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>

--- a/Översikt OLOFSTRÖM.xlsx
+++ b/Översikt OLOFSTRÖM.xlsx
@@ -601,7 +601,7 @@
         <v>45212</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44809</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>45629</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45268</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44559</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45581</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45583</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>45107</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45641</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45117</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>44858</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>44880</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44568</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>45625</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>45733</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45681</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>45141</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45098</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>45548</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45548</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45583</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45203</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>46050</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>46286</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>46302</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>46302</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>46070</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>46073</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>46087</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>44726</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>44726</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>44610</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>44610</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         <v>44755</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>44587</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>44572</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>44558</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>44853</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>44613</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>44613</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44613</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44699</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>44613</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>44567</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>44551</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>44551</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>44551</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>44866</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>44649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>44649</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>44496</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>44516</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>44866</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>44747</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>44551</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>44551</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>44551</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>44610</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>44686</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>44592</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>45700</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>44634</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>45078</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>45265</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>45112</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>45107</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>45701</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>45516</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45544</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>45194</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>45019</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>44809</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44889</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45162</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>45723</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>45233</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45011</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>45141</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45608</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>44531</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45233</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45699</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45032</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>44922</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>45385</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45233</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45282</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45197</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>44970</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45320</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>45243</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>45271</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>45268</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>45221</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>44866</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45582</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>45887</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>44965</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44965</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44942</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>45271</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>45183</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>45271</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>45268</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>44789</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>45274</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45891</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>45896</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45896</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45898</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>45571</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45163</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>45204</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>44531</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>45204</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>45898</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>45775</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45902</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>45902</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>45195</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>45603</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45036</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>45706</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>44873</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45548</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44536</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>44858</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>45195</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>44984</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>45371</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>45575</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45338</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45338</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45338</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45274</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45694</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45910</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>45720</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45268</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>45548</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45560</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>45583</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>45698</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>45401</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>45166</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>45595</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45733</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>45180</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>45274</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>45726</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>45338</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>45180</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>44581</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45120</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>44971</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>45527</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45602</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>44616</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>45699</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45698</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45112</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>45008</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>45930</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44971</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>44582</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>44832</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44951</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>45551</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45594</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45166</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45552</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45796</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>45247</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45177</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>44876</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>44970</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>44974</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44974</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45588</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>44748</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>45548</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45698</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>45733</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45803</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>45432</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45803</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45225</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>44622</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>44805</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45583</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45623</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45938</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>45940</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45719</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45268</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45141</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>44858</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>45623</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44935</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45629</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45594</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45593</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45827</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>45827</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>45827</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45693</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>45742</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>45700</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>45700</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>45956</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45602</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45639</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45963</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45166</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44704</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45965</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45282</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45238</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45967</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45707</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45707</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>44704</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45198</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>44858</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45645</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45247</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44791</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>44816</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45693</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45520</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45520</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45282</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>45707</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>45320</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>45168</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>45868</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45975</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45271</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>45282</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45169</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>45747</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>45747</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>45707</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45197</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>45742</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>45274</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>45274</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>44873</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45341</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>44879</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45071</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45246</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45565</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>46104</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>46106</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45723</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>46070</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45338</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45597</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45090</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45594</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>46119</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44552</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>46120</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>46125</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45548</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>44851</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44626</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>44743</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>46127</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45268</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>44935</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44862</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45245</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>44811</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45133</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45002</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45818</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45849</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45180</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45775</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45197</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45709</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45111</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>46013</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45883</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>44858</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>44590</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>45006</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44550</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>46027</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>46027</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45936</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45005</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45274</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45614</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45793</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45274</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45114</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45104</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44929</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45755</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45497</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45575</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44949</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>46050</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45407</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45012</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>46056</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45818</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>46003</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>46143</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45975</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>46065</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46059</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46059</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>46070</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>46078</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45849</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>46097</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45852</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>46169</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>46202</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>46202</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>46097</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>46269</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>46276</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>46280</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>46280</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>46280</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>46283</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>46286</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>46282</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>46284</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>46282</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>46286</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>46293</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>46293</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>46258</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>46300</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>46297</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>45903</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>46255</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>46042</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>45548</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>46261</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>45261</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44966</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>45016</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45827</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>45827</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45956</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>45956</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>44543</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>

--- a/Översikt OLOFSTRÖM.xlsx
+++ b/Översikt OLOFSTRÖM.xlsx
@@ -601,7 +601,7 @@
         <v>45212</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44809</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>45629</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45268</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44559</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45581</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45583</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>45107</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45641</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45117</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>44858</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>44880</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44568</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>45625</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>45733</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45681</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>45141</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45098</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>45548</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>45548</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>45583</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45203</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>45195</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>46050</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>46286</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>46302</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>46302</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>46070</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>46073</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>46087</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>44726</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>44610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>44726</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>44610</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>44610</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         <v>44755</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>44587</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>44572</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>44558</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>44853</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>44613</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>44613</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44613</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44699</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>44613</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>44567</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>44551</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>44551</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>44551</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>44866</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>44649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
         <v>44649</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         <v>44496</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>44516</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>44866</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>44747</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>44551</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>44551</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>44551</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>44610</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>44686</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>44592</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>45700</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>44634</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>45078</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>45265</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>45112</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>45107</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>45701</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>45516</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>45544</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7123,7 +7123,7 @@
         <v>45194</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>45019</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>44809</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         <v>44889</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>45162</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>45723</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>45233</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7634,7 +7634,7 @@
         <v>45011</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>45141</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>45608</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>44531</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45233</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45699</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45032</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>44922</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>45385</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>45233</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>45282</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>45197</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>44970</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>45320</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>45243</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>45271</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>45268</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>45221</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>44866</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45582</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>45887</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>44965</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44965</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44942</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>45271</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>45183</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>45271</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>45268</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>44789</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>45274</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>45891</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>45896</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>45896</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>45898</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>45571</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45163</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         <v>45204</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>44531</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>45204</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         <v>45898</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>45775</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45902</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>45902</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>45195</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>45603</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45036</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>45706</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11163,7 +11163,7 @@
         <v>44873</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45548</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44536</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>44858</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>45195</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>44984</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>45371</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         <v>45575</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>45338</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45338</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>45338</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45274</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45694</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12117,7 +12117,7 @@
         <v>45910</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>45720</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45268</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>45548</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45560</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>45583</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>45698</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>45401</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>45166</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>45595</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12852,7 +12852,7 @@
         <v>45733</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>45180</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>45274</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>45726</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13144,7 +13144,7 @@
         <v>45338</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13222,7 +13222,7 @@
         <v>45180</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13295,7 +13295,7 @@
         <v>44581</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>45120</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>44971</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>45527</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45602</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>44616</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>45699</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45698</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45112</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45203</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>45008</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>45930</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>44971</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>44582</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>44832</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>44951</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>45551</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45594</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45166</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45552</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45796</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>45247</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45177</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>44876</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>44970</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>44974</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44974</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45588</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>44748</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>45548</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45698</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>45733</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45803</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>45432</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45803</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45225</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>44622</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>44805</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45583</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45623</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45938</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>45940</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45719</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45268</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45141</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>44858</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>45623</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>44935</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>45629</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45594</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45593</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45827</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>45827</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17179,7 +17179,7 @@
         <v>45827</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45693</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>45742</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>45700</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>45700</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>45956</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45602</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45639</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45963</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45166</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>44704</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45965</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>45282</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>45238</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>45967</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45707</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45707</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>44704</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45198</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>44858</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45645</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45247</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44791</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>44816</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45693</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45520</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45520</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45282</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>45707</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>45320</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>45168</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>45868</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45975</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45271</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>45282</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45169</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>45747</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>45747</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>45707</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45197</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>45742</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>45274</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>45274</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>44873</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45341</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>44879</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45071</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45246</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45565</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>46104</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>46106</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45723</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>46070</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45338</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45597</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45090</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45594</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>46119</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44552</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>46120</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>46125</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45548</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>44851</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44626</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>44743</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>46127</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45268</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>44935</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
         <v>44862</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22246,7 +22246,7 @@
         <v>45245</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         <v>44811</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45133</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>45002</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>45818</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45849</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45180</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45775</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45197</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45709</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45111</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>46013</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45883</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>44858</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>44590</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>45006</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>44550</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>46027</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>46027</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45936</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45005</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45274</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>45614</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45793</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45274</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45114</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45104</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44929</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45755</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45497</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45575</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>44949</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>46050</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45407</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45012</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>46056</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45818</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>46003</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>46143</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45975</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>46065</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46059</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46059</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>46070</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>46078</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45849</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25609,7 +25609,7 @@
         <v>46097</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45852</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>46169</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>46202</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>46202</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>46097</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>46269</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>46276</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>46280</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26286,7 +26286,7 @@
         <v>46280</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         <v>46280</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>46283</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>46286</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>46282</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>46284</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>46282</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>46286</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26895,7 +26895,7 @@
         <v>46293</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>46293</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27051,7 +27051,7 @@
         <v>46258</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>46300</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27197,7 +27197,7 @@
         <v>46297</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27275,7 +27275,7 @@
         <v>45903</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27348,7 +27348,7 @@
         <v>46255</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>46042</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>45548</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27567,7 +27567,7 @@
         <v>46261</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>45261</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27713,7 +27713,7 @@
         <v>44966</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27786,7 +27786,7 @@
         <v>45016</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45827</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27937,7 +27937,7 @@
         <v>45827</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45956</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         <v>45956</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>44543</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>

--- a/Översikt OLOFSTRÖM.xlsx
+++ b/Översikt OLOFSTRÖM.xlsx
@@ -601,7 +601,7 @@
         <v>45212</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44809</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>45629</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45268</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44559</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45581</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>45583</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45641</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>44568</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>45195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45141</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>45583</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>45203</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45548</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>45548</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45098</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>45117</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44858</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>46050</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45733</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>46286</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45625</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>46302</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>46302</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>46070</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45681</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>46307</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>46073</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>46087</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>44726</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>44610</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>44726</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>44503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>44610</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>44610</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>44755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>44587</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44558</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>44572</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44853</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>44613</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>44567</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>44551</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>44866</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>44649</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>44649</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>44516</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44613</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>44699</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>44551</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>44551</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>44866</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>44551</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>44551</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>44551</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>44747</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>44496</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>44610</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>44686</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>44592</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>44634</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>45166</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>45597</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>45560</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>45162</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45169</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>44582</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>45271</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>45700</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>45548</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>45516</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>45002</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45180</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>44531</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>45552</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45645</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>45747</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>45747</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45693</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>44581</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44858</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45608</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>45183</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45168</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45071</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>45246</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45177</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45548</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>44971</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>45582</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44809</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>45544</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>45575</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>45274</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44858</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>44858</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44873</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44970</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>45623</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>45180</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>45623</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>45268</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45197</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>45221</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45203</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>45548</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45282</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>45233</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>45614</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>45775</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>45709</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>44832</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45818</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>44942</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>44951</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>45707</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44889</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>45887</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45891</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>45896</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45896</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>45114</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>45898</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>45898</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45936</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44935</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45497</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45793</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45111</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45902</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>45902</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>45818</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45775</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45198</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>45629</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>45910</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>46003</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45975</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>46143</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>45755</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>45707</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>45707</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
         <v>45265</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45699</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>44626</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>45930</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>45274</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>45166</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>44866</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45012</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45938</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44704</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>45940</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>45719</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45723</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>45551</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>44935</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45371</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>45956</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>45706</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>45849</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45520</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>45520</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45594</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>45965</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45963</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45195</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45852</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45594</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45967</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>44791</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>45407</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45602</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45975</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>44811</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>45006</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>45112</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45268</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>44929</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45341</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>45548</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>45011</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>45565</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>45238</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>46169</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>44879</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>45245</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45720</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45271</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45271</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45268</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45268</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45700</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>46013</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>44531</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>46027</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>46027</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44704</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>45274</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>44552</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>45698</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45166</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>46050</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>44876</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>45036</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>46056</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>46065</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45742</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>46059</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>46059</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>45583</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45268</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>46070</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>44992</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>46078</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45401</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>44873</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45595</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45247</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45247</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>44949</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>46097</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>45225</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45274</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45274</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>45197</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>44858</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>46104</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>46106</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>46070</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45282</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44965</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>44965</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>45090</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>46119</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>46202</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>46120</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45005</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>46125</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44743</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>46202</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>45338</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>45338</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45338</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>46127</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44748</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>45197</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44862</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>45849</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>45883</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45133</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44971</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45701</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>44805</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44536</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45233</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45588</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45699</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>44590</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>45120</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>46097</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45195</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45194</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>45274</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45274</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>45385</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>45527</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45575</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45141</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>44970</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>46276</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45320</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45271</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>46280</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>46280</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>46280</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45603</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>45707</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45008</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45104</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>44816</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>46283</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>44622</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>46282</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>46282</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45233</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44550</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45163</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44789</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>46286</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>46286</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45593</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45282</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>46284</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45078</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45019</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45204</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45204</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45639</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45141</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>44616</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45700</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45180</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44851</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45243</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44922</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>46293</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44974</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>44974</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>45723</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>45571</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>46293</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45032</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45320</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45594</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45903</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45602</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45693</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>46297</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45112</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44984</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>46255</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45282</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45107</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>45338</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>45694</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>46300</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>46258</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>46042</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>45726</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45583</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45338</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45698</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45733</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45548</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45796</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45733</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>46261</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45698</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45803</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45803</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45432</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>46311</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>46311</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>46311</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>46269</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>46311</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>46311</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>46311</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>46311</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45827</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>46311</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>45742</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>45827</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45827</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45868</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45261</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>44966</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>45016</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45827</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45827</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45956</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>45956</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>44543</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>

--- a/Översikt OLOFSTRÖM.xlsx
+++ b/Översikt OLOFSTRÖM.xlsx
@@ -601,7 +601,7 @@
         <v>45212</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44809</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>45629</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45268</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44559</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45581</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>45107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>45583</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45641</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>44568</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>45195</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45141</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>45583</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2367,7 +2367,7 @@
         <v>45203</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45548</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>45548</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45098</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>45117</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
         <v>44858</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
         <v>46050</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>45733</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>46286</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>45625</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>46302</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>46302</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>46070</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45681</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>46307</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>46073</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>46087</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>44726</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>44610</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>44726</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>44503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>44610</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>44610</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>44755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>44587</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44558</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>44572</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44853</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>44613</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>44567</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>44551</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>44866</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>44649</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>44649</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>44516</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44613</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>44699</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>44551</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>44551</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>44866</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>44551</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>44551</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>44551</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>44747</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>44496</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>44610</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>44686</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>44592</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>44634</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>45166</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>45597</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>45560</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>45162</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45169</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>44582</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>45271</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>45700</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>45548</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>45516</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>45002</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45180</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>44531</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>45552</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45645</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>45747</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>45747</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45693</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>44581</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44858</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45608</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>45183</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45168</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45071</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>45246</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45177</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45548</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>44971</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>45582</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44809</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>45544</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>45575</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>45274</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44858</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>44858</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44873</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44970</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>45623</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>45180</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>45623</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>45268</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45197</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>45221</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45203</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>45548</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45282</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>45233</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>45614</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>45775</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>45709</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>44832</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>45818</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>44942</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>44951</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>45707</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44889</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>45887</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45891</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>45896</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45896</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>45114</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>45898</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>45898</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>45936</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44935</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45497</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45793</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45111</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45902</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>45902</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>45818</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>45775</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45198</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>45629</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>45910</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>46003</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45975</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>46143</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>45755</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>45707</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12494,7 +12494,7 @@
         <v>45707</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12567,7 +12567,7 @@
         <v>45265</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>45699</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>44626</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>45930</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>45274</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>45166</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>44866</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45012</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>45938</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13224,7 +13224,7 @@
         <v>44704</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>45940</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>45719</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>45723</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>45551</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>44935</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>45371</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>45956</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>45706</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>45849</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45520</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>45520</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>45594</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>45965</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>45963</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>45195</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45852</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45594</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45967</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>44791</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14704,7 +14704,7 @@
         <v>45407</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45602</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45975</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>44811</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14996,7 +14996,7 @@
         <v>45006</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>45112</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45268</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>44929</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>45341</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>45548</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>45011</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>45565</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>45238</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>46169</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>44879</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>45245</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45720</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45271</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45271</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45268</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45268</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>45700</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>46013</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>44531</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>46027</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>46027</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>44704</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>45274</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>44552</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>45698</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45166</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>46050</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>44876</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>45036</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>46056</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>46065</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45742</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>46059</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>46059</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>45583</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45268</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>46070</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>44992</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>46078</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45401</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>44873</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45595</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45247</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45247</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>44949</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>46097</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>45225</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>45274</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45274</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>45197</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>44858</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>46104</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>46106</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>46070</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>45282</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>44965</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>44965</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>45090</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>46119</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>46202</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>46120</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45005</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>46125</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44743</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>46202</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>45338</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>45338</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45338</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>46127</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>44748</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>45197</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>44862</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>45849</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>45883</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45133</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>44971</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45701</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>44805</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44536</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45233</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45588</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45699</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>44590</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>45120</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>46097</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>45195</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45194</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>45274</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45274</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>45385</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>45527</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45575</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45141</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>44970</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>46276</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45320</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45271</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>46280</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>46280</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>46280</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22434,7 +22434,7 @@
         <v>45603</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>45707</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45008</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45104</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>44816</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>46283</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>44622</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>46282</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>46282</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45233</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44550</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45163</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44789</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>46286</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>46286</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>45593</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45282</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>46284</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45078</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45019</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45204</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45204</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45639</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45141</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>44616</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45700</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45180</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>44851</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24493,7 +24493,7 @@
         <v>45243</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44922</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>46293</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44974</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>44974</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>45723</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>45571</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>46293</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45032</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45320</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45594</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45903</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45602</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45693</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>46297</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45112</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44984</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>46255</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45282</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45107</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>45338</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>45694</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>46300</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>46258</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>46042</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>45726</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45583</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45338</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45698</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45733</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45548</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45796</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45733</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>46261</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>45698</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45803</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45803</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45432</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
         <v>46311</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27370,7 +27370,7 @@
         <v>46311</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>46311</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>46269</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>46311</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>46311</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>46311</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>46311</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>45827</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>46311</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>45742</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>45827</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45827</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>45868</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45261</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>44966</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>45016</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45827</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45827</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>45956</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28782,7 +28782,7 @@
         <v>45956</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         <v>44543</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>

--- a/Översikt OLOFSTRÖM.xlsx
+++ b/Översikt OLOFSTRÖM.xlsx
@@ -601,7 +601,7 @@
         <v>45212</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44809</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>45629</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45268</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44559</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45583</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>45107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45641</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>45581</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45203</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45195</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45117</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44858</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44880</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45625</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>46286</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>46050</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45681</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>46302</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>46302</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>46070</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>45583</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>46307</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>45098</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44568</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45733</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45141</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45548</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45548</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>46073</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>46087</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>44726</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>44610</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>44726</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>44503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>44610</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>44610</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>44755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>44587</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44558</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>44572</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44853</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>44613</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>44567</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>44551</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>44866</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>44649</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>44649</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>44516</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44613</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>44699</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>44551</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>44551</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>44866</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>44551</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>44551</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>44551</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>44747</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>44496</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>44610</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>44686</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>44935</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>44592</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>44634</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>45887</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>45245</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>44811</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45194</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>45891</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>45002</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>45180</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>45197</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>45896</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>45896</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45898</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>45032</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>45111</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45898</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>45775</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>45902</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45902</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>44858</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44590</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45006</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44550</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45910</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45005</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>45274</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45852</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45614</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>45274</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>45114</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>45104</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>45699</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>46169</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>45930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44929</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>45755</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>45575</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44949</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>45701</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>45407</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>45938</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>45012</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>45940</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>45719</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45078</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>44992</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>45516</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>45544</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>45019</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>44809</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>45162</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>45723</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>45233</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>45956</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45963</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>45141</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>45608</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>44531</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45233</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>45965</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45699</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>44922</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>45967</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>45975</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>46202</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>45221</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44866</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>46202</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>44965</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44965</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>45271</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>45183</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>44970</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45271</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>45268</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44789</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45274</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45571</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>45163</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>45204</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>45204</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>45195</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>45603</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>45036</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>45706</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>45320</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44536</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>46097</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45274</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>45694</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45583</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45698</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45733</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>46280</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>46013</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>46280</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>46280</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>45726</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>45338</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>46027</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>46027</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>46283</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>46286</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>46282</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>46284</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>45243</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>45271</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45268</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>46282</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>46286</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45796</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>46050</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>45698</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>45733</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45803</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>45432</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45803</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>46056</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>44942</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>46065</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>46059</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>46059</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>46293</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>46070</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>46293</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>46078</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45827</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45827</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45827</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>45742</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>46258</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>46300</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>46297</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>46097</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>46255</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44531</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>46104</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>46106</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>46070</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>46042</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>44873</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>45868</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>46119</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>45548</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>46120</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>46125</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>46261</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45195</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>44743</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>46127</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>44984</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>45371</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>45548</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>44862</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45560</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45133</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45818</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45849</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45775</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45709</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45883</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>46311</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45936</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>46311</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>44971</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>44616</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45793</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>46269</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45112</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>46311</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>46311</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>46315</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>46315</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44971</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>46315</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>46311</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>46311</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>46311</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>46311</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>46315</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45497</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>44951</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45247</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>44876</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>44970</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>46276</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>44974</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>44974</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45588</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45818</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45548</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>46003</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>46143</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45975</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45225</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44622</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45268</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45849</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45623</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44935</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>45629</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45594</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45593</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45602</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45639</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45238</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>44704</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45645</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44791</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45693</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45707</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45168</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>45169</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45747</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45747</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45707</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45197</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45742</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44879</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45071</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45246</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45565</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45723</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>45338</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45090</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45594</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>45700</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45265</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45112</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45107</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44889</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>45011</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>45385</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45233</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>45282</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45197</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45582</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>44858</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>45575</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45338</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45338</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>45338</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45720</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>45268</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45548</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45401</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45166</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45595</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45180</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>45274</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>45180</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44581</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45120</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45527</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45602</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45698</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45203</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>45008</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>44582</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>44832</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>45551</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45594</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>45166</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45552</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45177</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>44748</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44805</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45583</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45623</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45141</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44858</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45693</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45700</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45700</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45166</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44704</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>45282</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45707</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>45707</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45198</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44858</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>45247</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>44816</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>45520</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45520</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45282</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45320</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>45271</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>45282</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45274</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>45274</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>44873</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>45341</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45597</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>44552</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>45548</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>44851</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>44626</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>45268</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45261</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>44966</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>45016</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45827</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>45827</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>45956</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>45956</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>44543</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>

--- a/Översikt OLOFSTRÖM.xlsx
+++ b/Översikt OLOFSTRÖM.xlsx
@@ -601,7 +601,7 @@
         <v>45212</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>44809</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45133</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>45629</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>45268</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44559</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>45583</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>45107</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>45641</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>45581</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45203</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45195</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45117</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>44858</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>44880</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45625</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>46286</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>46050</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45681</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>46302</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>46302</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>46070</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>45583</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>46307</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>45098</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44568</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45733</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>45141</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>45548</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>45548</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>46073</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>46087</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>44726</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>44610</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>44726</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>44503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>44610</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>44610</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>44755</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>44587</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>44558</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>44572</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>44853</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>44613</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>44567</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>44551</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         <v>44866</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5257,7 +5257,7 @@
         <v>44649</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
         <v>44649</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>44516</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         <v>44613</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>44699</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>44551</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>44551</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>44866</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>44551</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>44551</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>44551</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>44747</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>44496</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>44610</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         <v>44686</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>44935</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>44592</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>44634</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>45887</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>45245</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>44811</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45194</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>45891</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>45002</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>45180</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>45197</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>45896</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>45896</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45898</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>45032</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>45111</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45898</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>45775</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>45902</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45902</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>44858</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44590</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45006</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>44550</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>45910</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45005</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>45274</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>45852</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>45614</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>45274</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>45114</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>45104</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>45699</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>46169</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8980,7 +8980,7 @@
         <v>45930</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>44929</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         <v>45755</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>45575</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44949</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>45701</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>45407</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>45938</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>45012</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>45940</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>45719</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45078</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>44992</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>45516</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>45544</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>45019</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         <v>44809</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>45162</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>45723</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>45233</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>45956</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45963</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>45141</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10664,7 +10664,7 @@
         <v>45608</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10737,7 +10737,7 @@
         <v>44531</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>45233</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>45965</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>45699</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>44922</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>45967</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>45975</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
         <v>46202</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>45221</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44866</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>46202</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>44965</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44965</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>45271</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>45183</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11837,7 +11837,7 @@
         <v>44970</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45271</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>45268</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44789</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45274</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45571</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>45163</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>45204</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>45204</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>45195</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>45603</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>45036</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12723,7 +12723,7 @@
         <v>45706</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>45320</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44536</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>46097</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45274</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>45694</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45583</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45698</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45733</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>46280</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>46013</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>46280</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>46280</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>45726</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>45338</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         <v>46027</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>46027</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>46283</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>46286</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>46282</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>46284</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>45243</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>45271</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45268</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>46282</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>46286</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45796</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>46050</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>45698</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>45733</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45803</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>45432</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>45803</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15182,7 +15182,7 @@
         <v>46056</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15255,7 +15255,7 @@
         <v>44942</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>46065</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>46059</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>46059</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>46293</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>46070</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>46293</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>46078</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45827</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45827</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45827</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>45742</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>46258</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>46300</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>46297</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>46097</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>46255</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>44531</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>46104</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>46106</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>46070</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>46042</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>44873</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>45868</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>46119</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
         <v>45548</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>46120</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>46125</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>46261</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17407,7 +17407,7 @@
         <v>45195</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17480,7 +17480,7 @@
         <v>44743</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
         <v>46127</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         <v>44984</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>45371</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>45548</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17845,7 +17845,7 @@
         <v>44862</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>45560</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17991,7 +17991,7 @@
         <v>45133</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>45818</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45849</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45775</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45709</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45883</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
         <v>46311</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45936</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>46311</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>44971</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>44616</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45793</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>46269</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45112</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>46311</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>46311</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>46315</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>46315</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44971</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>46315</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>46311</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>46311</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>46311</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>46311</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>46315</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45497</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>44951</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45247</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>44876</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>44970</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>46276</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>44974</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>44974</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45588</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45818</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45548</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>46003</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>46143</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45975</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45225</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44622</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45268</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45849</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45623</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44935</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>45629</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45594</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45593</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45602</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45639</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45238</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>44704</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>45645</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44791</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45693</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45707</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>45168</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>45169</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
         <v>45747</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45747</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22391,7 +22391,7 @@
         <v>45707</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45197</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45742</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>44879</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45071</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45246</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45565</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22902,7 +22902,7 @@
         <v>45723</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -22975,7 +22975,7 @@
         <v>45338</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45090</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45594</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>45700</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23267,7 +23267,7 @@
         <v>45265</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45112</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>45107</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>44889</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>45011</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>45385</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45233</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>45282</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45197</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45582</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>44858</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>45575</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45338</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45338</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24294,7 +24294,7 @@
         <v>45338</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24367,7 +24367,7 @@
         <v>45720</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>45268</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
         <v>45548</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24591,7 +24591,7 @@
         <v>45401</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24664,7 +24664,7 @@
         <v>45166</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45595</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45180</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>45274</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>45180</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>44581</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45120</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25175,7 +25175,7 @@
         <v>45527</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45602</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45698</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45203</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25467,7 +25467,7 @@
         <v>45008</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25540,7 +25540,7 @@
         <v>44582</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25613,7 +25613,7 @@
         <v>44832</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>45551</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>45594</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25832,7 +25832,7 @@
         <v>45166</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>45552</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>45177</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>44748</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26124,7 +26124,7 @@
         <v>44805</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>45583</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26270,7 +26270,7 @@
         <v>45623</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26343,7 +26343,7 @@
         <v>45141</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         <v>44858</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45693</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26562,7 +26562,7 @@
         <v>45700</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45700</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45166</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>44704</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>45282</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45707</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>45707</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45198</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>44858</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>45247</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>44816</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>45520</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>45520</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45282</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45320</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27667,7 +27667,7 @@
         <v>45271</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>45282</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>45274</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>45274</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>44873</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>45341</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45597</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>44552</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>45548</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>44851</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>44626</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>45268</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45261</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>44966</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>45016</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45827</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>45827</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>45956</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>45956</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29079,7 +29079,7 @@
         <v>44543</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
